--- a/templates/28-metrics-and-key-performance-indicators-template.xlsx
+++ b/templates/28-metrics-and-key-performance-indicators-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Blank template" sheetId="2" r:id="rId2"/>
+    <sheet name="Blank template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -448,114 +447,6 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.28  Metrics and Key Performance Indicators</t>
-        </is>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Measurement and evaluation</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What it is for</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defines what will be measured, how, how often and against what target, so performance can be judged rather than asserted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when success has been described in adjectives, or when data is being collected that nobody has tied to an objective.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confused with</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A metric is a raw measure; a KPI is a metric tied to an objective with a target. An indicator that nobody would act on is a metric, not a KPI, however prominently it is displayed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8.1 Measure Solution Performance  ·  8.2 Analyze Performance Measures  ·  6.2 Define Future State</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge areas</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6, 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The blank template is on the next sheet — fill it in.</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
